--- a/resources/templates/standard/B1100-03.xlsx
+++ b/resources/templates/standard/B1100-03.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>특채 의뢰서(갑지)</t>
   </si>
@@ -732,13 +735,15 @@
   <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="2.125" customHeight="1"/>
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
@@ -767,23 +772,23 @@
       <c r="AE1" s="2"/>
       <c r="AF1" s="2"/>
       <c r="AG1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH1" s="3"/>
       <c r="AI1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ1" s="4"/>
       <c r="AK1" s="4"/>
       <c r="AL1" s="4"/>
       <c r="AM1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN1" s="4"/>
       <c r="AO1" s="4"/>
       <c r="AP1" s="4"/>
       <c r="AQ1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR1" s="4"/>
       <c r="AS1" s="4"/>
@@ -839,10 +844,10 @@
     </row>
     <row r="3" ht="24.95" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -860,7 +865,7 @@
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
@@ -876,7 +881,7 @@
       <c r="AD3" s="7"/>
       <c r="AE3" s="7"/>
       <c r="AF3" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG3" s="4"/>
       <c r="AH3" s="4"/>
@@ -896,7 +901,7 @@
     <row r="4" ht="24.95" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
       <c r="B4" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -919,7 +924,7 @@
       <c r="U4" s="9"/>
       <c r="V4" s="9"/>
       <c r="W4" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X4" s="8"/>
       <c r="Y4" s="8"/>
@@ -935,7 +940,7 @@
       <c r="AI4" s="10"/>
       <c r="AJ4" s="10"/>
       <c r="AK4" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL4" s="8"/>
       <c r="AM4" s="8"/>
@@ -950,7 +955,7 @@
     <row r="5" ht="24.95" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -968,7 +973,7 @@
       <c r="P5" s="9"/>
       <c r="Q5" s="9"/>
       <c r="R5" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S5" s="8"/>
       <c r="T5" s="8"/>
@@ -1002,7 +1007,7 @@
     <row r="6" ht="27.95" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
@@ -1244,7 +1249,7 @@
     <row r="11" ht="27.95" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -1437,10 +1442,10 @@
     </row>
     <row r="15" ht="32.1" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
@@ -1481,7 +1486,7 @@
       <c r="AM15" s="15"/>
       <c r="AN15" s="15"/>
       <c r="AO15" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP15" s="3"/>
       <c r="AQ15" s="7"/>
@@ -1531,7 +1536,7 @@
       <c r="AM16" s="16"/>
       <c r="AN16" s="16"/>
       <c r="AO16" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP16" s="17"/>
       <c r="AQ16" s="9"/>
@@ -1542,7 +1547,7 @@
     <row r="17" ht="32.1" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A17" s="14"/>
       <c r="B17" s="18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" s="18"/>
       <c r="D17" s="18"/>
@@ -1583,7 +1588,7 @@
       <c r="AM17" s="18"/>
       <c r="AN17" s="18"/>
       <c r="AO17" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP17" s="17"/>
       <c r="AQ17" s="9"/>
@@ -1633,7 +1638,7 @@
       <c r="AM18" s="19"/>
       <c r="AN18" s="19"/>
       <c r="AO18" s="20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP18" s="20"/>
       <c r="AQ18" s="21"/>
@@ -1691,31 +1696,31 @@
     </row>
     <row r="20" ht="24.95" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M20" s="4"/>
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
       <c r="P20" s="4"/>
       <c r="Q20" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R20" s="4"/>
       <c r="S20" s="4"/>
@@ -1725,11 +1730,11 @@
       <c r="W20" s="4"/>
       <c r="X20" s="4"/>
       <c r="Y20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z20" s="3"/>
       <c r="AA20" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB20" s="22"/>
       <c r="AC20" s="22"/>
@@ -1742,7 +1747,7 @@
       <c r="AJ20" s="22"/>
       <c r="AK20" s="22"/>
       <c r="AL20" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM20" s="3"/>
       <c r="AN20" s="22"/>
@@ -1819,7 +1824,7 @@
       <c r="O22" s="9"/>
       <c r="P22" s="9"/>
       <c r="Q22" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R22" s="9"/>
       <c r="S22" s="9"/>
@@ -1869,7 +1874,7 @@
       <c r="O23" s="9"/>
       <c r="P23" s="9"/>
       <c r="Q23" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R23" s="9"/>
       <c r="S23" s="9"/>
@@ -1904,7 +1909,7 @@
     <row r="24" ht="24.95" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>
       <c r="B24" s="23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C24" s="23"/>
       <c r="D24" s="23"/>
@@ -1921,7 +1926,7 @@
       <c r="O24" s="23"/>
       <c r="P24" s="23"/>
       <c r="Q24" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R24" s="8"/>
       <c r="S24" s="8"/>
@@ -1938,7 +1943,7 @@
       <c r="AD24" s="9"/>
       <c r="AE24" s="9"/>
       <c r="AF24" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AG24" s="8"/>
       <c r="AH24" s="8"/>
@@ -1958,7 +1963,7 @@
     <row r="25" ht="75" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A25" s="6"/>
       <c r="B25" s="24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C25" s="24"/>
       <c r="D25" s="24"/>
@@ -2008,7 +2013,7 @@
     <row r="26" ht="24.75" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A26" s="6"/>
       <c r="B26" s="25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
@@ -2105,10 +2110,10 @@
     </row>
     <row r="28" ht="24.75" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C28" s="27"/>
       <c r="D28" s="27"/>
@@ -2140,21 +2145,21 @@
       <c r="AD28" s="27"/>
       <c r="AE28" s="27"/>
       <c r="AF28" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AG28" s="4"/>
       <c r="AH28" s="4"/>
       <c r="AI28" s="4"/>
       <c r="AJ28" s="4"/>
       <c r="AK28" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL28" s="4"/>
       <c r="AM28" s="4"/>
       <c r="AN28" s="4"/>
       <c r="AO28" s="4"/>
       <c r="AP28" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ28" s="4"/>
       <c r="AR28" s="4"/>
